--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-medication-administration.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -766,7 +770,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1731,13 +1735,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1788,7 +1792,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1805,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1831,13 +1835,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1888,7 +1892,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1905,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1931,13 +1935,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1988,7 +1992,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2005,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2031,13 +2035,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2088,7 +2092,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2105,10 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2131,13 +2135,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2188,7 +2192,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2205,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2231,13 +2235,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2288,7 +2292,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2305,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2331,13 +2335,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2388,7 +2392,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2405,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2431,13 +2435,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2488,7 +2492,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2505,10 +2509,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2531,13 +2535,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2588,7 +2592,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2605,10 +2609,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2631,13 +2635,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2688,7 +2692,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -2705,10 +2709,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2731,13 +2735,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2788,7 +2792,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="153">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-medication-administration.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-medication-administration.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-medication-administration.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-medication-administration.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-medication-administration.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-medication-administration.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-medication-administration.header.source</t>
+    <t>fr-lm-medication-administration.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-administration.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,16 +452,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-administration.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut, completed</t>
   </si>
   <si>
     <t>fr-lm-medication-administration.dureeTraitement</t>
@@ -757,11 +789,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.57421875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.57421875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="62.28125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="62.28125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -770,7 +802,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.25" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -784,14 +816,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.7265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1535,13 +1567,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1592,7 +1624,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1609,10 +1641,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1635,13 +1667,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1692,7 +1724,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1709,10 +1741,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1735,13 +1767,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1792,7 +1824,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1809,10 +1841,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1835,7 +1867,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1935,13 +1967,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1992,7 +2024,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2009,10 +2041,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2023,7 +2055,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2035,13 +2067,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2092,13 +2124,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2109,10 +2141,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2123,7 +2155,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2135,13 +2167,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2192,13 +2224,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2209,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2223,7 +2255,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2235,13 +2267,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2292,13 +2324,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2309,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2320,7 +2352,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2335,13 +2367,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2392,10 +2424,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2409,10 +2441,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2420,7 +2452,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2435,7 +2467,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>132</v>
@@ -2471,10 +2503,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2492,10 +2524,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2509,10 +2541,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2535,13 +2567,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2592,7 +2624,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2609,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2620,7 +2652,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2635,13 +2667,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2692,10 +2724,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2709,10 +2741,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2723,7 +2755,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2735,13 +2767,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2792,18 +2824,318 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-administration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
